--- a/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
+++ b/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mattarello, Via Torrefranca, fermata Bus al parco</t>
+          <t>Aldeno, Via Filzi, Fermata corriere</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC ALDENO-MATTARELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Malé, Stazione FTM</t>
+          <t>Mattarello, Via Torrefranca, fermata Bus al parco</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,42 +496,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC BRENTONICO</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSPG, Via F. Calzolari, 2, Brentonico</t>
+          <t>Malé, Stazione FTM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC BRENTONICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cavalese, stazione autocorriere</t>
+          <t>SSPG, Via F. Calzolari, 2, Brentonico</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ponte Arche, Via S. Giovanni Bosco, 14</t>
+          <t>Cavalese, stazione autocorriere</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Ponte Arche, Via S. Giovanni Bosco, 14</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lavis, Via Carlo Sette, 13/A</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,31 +571,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mezzocorona, Via Fornai 1</t>
+          <t>Lavis, Via Carlo Sette, 13/A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Andalo, Piazza San Vito, 1</t>
+          <t>Mezzocorona, Via Fornai 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -606,7 +606,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via degli Alpini, 17</t>
+          <t>Andalo, Piazza San Vito, 1</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spormaggiore, Fermata bus</t>
+          <t>Mezzolombardo, Via degli Alpini, 17</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,42 +631,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pergine, Via Dante, Fermata Tentazioni</t>
+          <t>Spormaggiore, Fermata bus</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvallazione, 44</t>
+          <t>Pergine, Via Dante, Fermata Tentazioni</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC TRENTO SACRO CUORE</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,210 +676,375 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Madonna di Campiglio, Piazzale Brenta, Loc. Palù</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pinzolo, Viale della Pace, 10</t>
+          <t>Tione, Via Circonvallazione, 44</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO SACRO CUORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spiazzo, Frazione Fisto, 108</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC VIGOLO VATTARO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fermata bus - Vigolo Vattaro</t>
+          <t>Madonna di Campiglio, Piazzale Brenta, Loc. Palù</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC VILLA LAGARINA</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
+          <t>Pinzolo, Viale della Pace, 10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IS ENAIP CLES</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Spiazzo, Frazione Fisto, 108</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IS ENAIP OSSANA</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ossana, Via S. Antonio</t>
+          <t>Fermata bus - Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IS GUETTI TIONE</t>
+          <t>IC VILLA LAGARINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tione, Stazione autocorriere</t>
+          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS MAFFEI RIVA DEL GARDA</t>
+          <t>IS ENAIP CLES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Riva del Garda, Stazione autocorriere</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS ENAIP OSSANA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovereto, Via Monti, 1</t>
+          <t>Ossana, Via S. Antonio</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IS ENAIP TIONE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Predazzo, Fermata Bus Corso Degasperi</t>
+          <t>Tione, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS ENAIP VILLAZZANO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IS TRENTO TAMBOSI</t>
+          <t>IS FILZI ROVERETO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>IS FONTANA ROVERETO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IS GUETTI TIONE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tione, Stazione autocorriere</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IS LINGUISTICO SCHOLL TRENTO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Trento, Park Area Ex Italcementi</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IS MAFFEI RIVA DEL GARDA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Riva del Garda, Stazione autocorriere</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IS MARCONI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rovereto, Via Monti, 1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IS PERTINI TRENTO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Trento, Park Area Ex Italcementi</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cavalese, stazione autocorriere</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Predazzo, Fermata Bus Corso Degasperi</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IS ROSMINI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IS TIONE GUETTI-Students staff</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tione, Stazione autocorriere</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IS TRENTO TAMBOSI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Trento, Park Area Ex Italcementi</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>IS VITTORIA BONPORTI TRENTO</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C42" t="n">
         <v>17</v>
       </c>
     </row>

--- a/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
+++ b/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via Betta, Ala</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
+++ b/tests/realSuite/Sci-alpino-School_IC-IS_28-gen-2026_CON-VETTORI/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aldeno, Via Filzi, Fermata corriere</t>
+          <t>Malé, Stazione FTM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC BRENTONICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mattarello, Via Torrefranca, fermata Bus al parco</t>
+          <t>SSPG, Via F. Calzolari, 2, Brentonico</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Malé, Stazione FTM</t>
+          <t>Cavalese, stazione autocorriere</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -511,27 +511,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC BRENTONICO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSPG, Via F. Calzolari, 2, Brentonico</t>
+          <t>Ponte Arche, Via S. Giovanni Bosco, 14</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cavalese, stazione autocorriere</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ponte Arche, Via S. Giovanni Bosco, 14</t>
+          <t>Lavis, Via Carlo Sette, 13/A</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,46 +556,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Mezzocorona, Via Fornai 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lavis, Via Carlo Sette, 13/A</t>
+          <t>Andalo, Piazza San Vito, 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mezzocorona, Via Fornai 1</t>
+          <t>Mezzolombardo, Via degli Alpini, 17</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -606,7 +606,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Andalo, Piazza San Vito, 1</t>
+          <t>Spormaggiore, Fermata bus</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,106 +616,106 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via degli Alpini, 17</t>
+          <t>Pergine, Via Dante, Fermata Tentazioni</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spormaggiore, Fermata bus</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pergine, Via Dante, Fermata Tentazioni</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Tione, Via Circonvallazione, 44</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC TRENTO SACRO CUORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tione, Via Circonvallazione, 44</t>
+          <t>Madonna di Campiglio, Piazzale Brenta, Loc. Palù</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC TRENTO SACRO CUORE</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Pinzolo, Viale della Pace, 10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -726,325 +726,295 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Madonna di Campiglio, Piazzale Brenta, Loc. Palù</t>
+          <t>Spiazzo, Frazione Fisto, 108</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pinzolo, Viale della Pace, 10</t>
+          <t>Fermata bus - Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VILLA LAGARINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spiazzo, Frazione Fisto, 108</t>
+          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC VIGOLO VATTARO</t>
+          <t>IS ENAIP CLES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fermata bus - Vigolo Vattaro</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC VILLA LAGARINA</t>
+          <t>IS ENAIP OSSANA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSPG - Via Stockstadt am Rhein, 3, Villa Lagarina</t>
+          <t>Ossana, Via S. Antonio</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS ENAIP CLES</t>
+          <t>IS ENAIP TIONE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Tione, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS ENAIP OSSANA</t>
+          <t>IS ENAIP VILLAZZANO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ossana, Via S. Antonio</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IS ENAIP TIONE</t>
+          <t>IS FILZI ROVERETO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tione, Stazione autocorriere</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IS ENAIP VILLAZZANO</t>
+          <t>IS FONTANA ROVERETO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IS FILZI ROVERETO</t>
+          <t>IS GUETTI TIONE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Tione, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IS FONTANA ROVERETO</t>
+          <t>IS LINGUISTICO SCHOLL TRENTO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IS GUETTI TIONE</t>
+          <t>IS MAFFEI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tione, Stazione autocorriere</t>
+          <t>Riva del Garda, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IS LINGUISTICO SCHOLL TRENTO</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Rovereto, Via Monti, 1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IS MAFFEI RIVA DEL GARDA</t>
+          <t>IS PERTINI TRENTO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Riva del Garda, Stazione autocorriere</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS ROSA BIANCA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rovereto, Via Monti, 1</t>
+          <t>Cavalese, stazione autocorriere</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IS PERTINI TRENTO</t>
+          <t>IS ROSA BIANCA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Predazzo, Fermata Bus Corso Degasperi</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IS ROSMINI ROVERETO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cavalese, stazione autocorriere</t>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IS TIONE GUETTI-Students staff</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Predazzo, Fermata Bus Corso Degasperi</t>
+          <t>Tione, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS TRENTO TAMBOSI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IS TIONE GUETTI-Students staff</t>
+          <t>IS VITTORIA BONPORTI TRENTO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tione, Stazione autocorriere</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>IS TRENTO TAMBOSI</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Trento, Park Area Ex Italcementi</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>IS VITTORIA BONPORTI TRENTO</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trento, Park Area Ex Italcementi</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
         <v>17</v>
       </c>
     </row>
